--- a/data/trans_camb/IP19C07-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP19C07-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 7,27</t>
+          <t>-10,65; 6,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 3,18</t>
+          <t>-13,16; 3,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,36; 3,74</t>
+          <t>-14,44; 3,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,67; 2,81</t>
+          <t>-14,8; 3,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,38; 0,56</t>
+          <t>-16,61; -0,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,95; -6,97</t>
+          <t>-21,53; -7,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 1,85</t>
+          <t>-10,61; 2,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,82; -1,08</t>
+          <t>-12,72; -0,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,17; -4,24</t>
+          <t>-15,25; -4,43</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-61,47; 92,62</t>
+          <t>-60,8; 79,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-74,99; 41,16</t>
+          <t>-74,59; 46,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-79,73; 56,63</t>
+          <t>-81,28; 48,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-72,71; 37,21</t>
+          <t>-72,45; 35,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-81,84; 15,4</t>
+          <t>-81,55; 13,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-97,22; -50,28</t>
+          <t>-97,41; -56,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-59,3; 18,44</t>
+          <t>-59,11; 18,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-71,93; -3,31</t>
+          <t>-71,08; -4,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-85,16; -34,81</t>
+          <t>-85,78; -34,04</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 8,13</t>
+          <t>-3,79; 8,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 8,87</t>
+          <t>-4,79; 8,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 3,15</t>
+          <t>-8,13; 2,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 5,23</t>
+          <t>-6,72; 5,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,43; -1,55</t>
+          <t>-11,45; -1,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 1,9</t>
+          <t>-9,38; 1,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 5,87</t>
+          <t>-3,47; 5,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 2,1</t>
+          <t>-5,91; 2,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 0,43</t>
+          <t>-6,93; 1,05</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-37,83; 160,27</t>
+          <t>-35,23; 165,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,65; 176,19</t>
+          <t>-46,43; 146,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-75,09; 68,06</t>
+          <t>-78,9; 64,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-54,04; 90,65</t>
+          <t>-58,39; 89,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-89,58; -18,86</t>
+          <t>-90,83; -15,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-72,46; 35,9</t>
+          <t>-74,71; 34,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-33,63; 92,82</t>
+          <t>-31,99; 79,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,68; 33,38</t>
+          <t>-55,51; 36,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-67,33; 10,5</t>
+          <t>-64,19; 20,46</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 5,64</t>
+          <t>-9,56; 5,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,82; -0,04</t>
+          <t>-13,24; 0,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 7,1</t>
+          <t>-8,54; 6,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 8,18</t>
+          <t>-4,48; 9,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 5,37</t>
+          <t>-7,59; 4,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 7,82</t>
+          <t>-5,13; 7,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 5,3</t>
+          <t>-5,03; 5,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 1,09</t>
+          <t>-7,96; 1,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 5,28</t>
+          <t>-4,92; 5,04</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-65,98; 93,41</t>
+          <t>-68,63; 93,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-87,74; 11,73</t>
+          <t>-87,77; 6,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-62,16; 125,96</t>
+          <t>-59,9; 113,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-52,48; 219,35</t>
+          <t>-50,46; 259,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-70,49; 157,14</t>
+          <t>-73,87; 134,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-52,49; 219,26</t>
+          <t>-55,85; 197,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-46,04; 88,57</t>
+          <t>-45,02; 88,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-72,22; 23,34</t>
+          <t>-73,76; 26,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-40,22; 97,07</t>
+          <t>-44,41; 87,65</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-17,06; -0,63</t>
+          <t>-17,64; -1,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-17,5; -0,34</t>
+          <t>-16,37; 0,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,09; -0,22</t>
+          <t>-17,75; -0,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 11,19</t>
+          <t>-3,86; 11,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 4,76</t>
+          <t>-7,8; 5,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 3,76</t>
+          <t>-9,26; 3,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 3,14</t>
+          <t>-8,5; 2,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 0,35</t>
+          <t>-10,64; -0,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,77; -0,66</t>
+          <t>-11,19; -0,78</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-77,88; -2,82</t>
+          <t>-77,99; -9,29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-74,73; 5,46</t>
+          <t>-74,51; 2,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-75,02; 0,35</t>
+          <t>-77,05; 5,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-33,59; 222,84</t>
+          <t>-34,38; 219,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-63,02; 108,01</t>
+          <t>-62,68; 123,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-71,98; 78,33</t>
+          <t>-73,69; 64,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-52,51; 32,0</t>
+          <t>-52,08; 27,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-64,1; 3,14</t>
+          <t>-63,58; 0,36</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-66,74; -4,69</t>
+          <t>-68,46; -6,49</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 1,16</t>
+          <t>-6,6; 1,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,99; -0,41</t>
+          <t>-8,03; -0,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,38; -0,72</t>
+          <t>-8,19; -0,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 3,41</t>
+          <t>-3,89; 3,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,89; -1,37</t>
+          <t>-7,2; -0,97</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,92; -1,11</t>
+          <t>-7,31; -1,21</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 1,39</t>
+          <t>-3,95; 1,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,61; -1,63</t>
+          <t>-6,88; -1,98</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,05; -2,2</t>
+          <t>-6,95; -2,04</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-46,71; 11,65</t>
+          <t>-45,46; 14,07</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-56,74; -4,1</t>
+          <t>-54,28; -4,24</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-57,5; -5,63</t>
+          <t>-55,66; -8,06</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-32,19; 41,55</t>
+          <t>-32,63; 39,54</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-64,08; -14,62</t>
+          <t>-62,73; -11,96</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-62,67; -12,31</t>
+          <t>-62,02; -11,9</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-30,64; 13,27</t>
+          <t>-31,7; 11,17</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-52,34; -16,19</t>
+          <t>-53,69; -18,39</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-56,43; -22,85</t>
+          <t>-56,04; -20,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C07-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP19C07-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,65; 6,75</t>
+          <t>-11,16; 7,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 3,62</t>
+          <t>-12,96; 3,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 3,06</t>
+          <t>-13,84; 3,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,8; 3,26</t>
+          <t>-13,71; 4,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,61; -0,16</t>
+          <t>-16,62; 0,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-21,53; -7,15</t>
+          <t>-20,52; -5,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 2,05</t>
+          <t>-10,74; 2,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,72; -0,68</t>
+          <t>-12,46; -0,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,25; -4,43</t>
+          <t>-15,37; -4,11</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-60,8; 79,09</t>
+          <t>-62,77; 84,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-74,59; 46,69</t>
+          <t>-72,11; 46,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-81,28; 48,02</t>
+          <t>-80,67; 49,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-72,45; 35,81</t>
+          <t>-69,57; 42,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-81,55; 13,06</t>
+          <t>-81,36; 19,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-97,41; -56,0</t>
+          <t>-97,0; -49,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-59,11; 18,65</t>
+          <t>-60,18; 22,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-71,08; -4,31</t>
+          <t>-72,0; -0,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-85,78; -34,04</t>
+          <t>-85,68; -29,67</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 8,33</t>
+          <t>-3,89; 8,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 8,22</t>
+          <t>-4,42; 8,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 2,94</t>
+          <t>-8,32; 2,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 5,0</t>
+          <t>-7,04; 5,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,45; -1,94</t>
+          <t>-11,42; -1,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 1,82</t>
+          <t>-9,0; 1,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 5,24</t>
+          <t>-3,45; 5,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 2,17</t>
+          <t>-6,48; 1,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 1,05</t>
+          <t>-7,06; 0,8</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-35,23; 165,39</t>
+          <t>-37,34; 164,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-46,43; 146,45</t>
+          <t>-41,91; 176,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-78,9; 64,04</t>
+          <t>-75,11; 79,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-58,39; 89,12</t>
+          <t>-58,07; 77,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-90,83; -15,76</t>
+          <t>-89,81; -13,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-74,71; 34,2</t>
+          <t>-73,05; 30,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,99; 79,0</t>
+          <t>-32,03; 80,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,51; 36,33</t>
+          <t>-58,77; 26,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-64,19; 20,46</t>
+          <t>-65,07; 14,18</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 5,82</t>
+          <t>-9,32; 5,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 0,04</t>
+          <t>-13,53; 0,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 6,38</t>
+          <t>-7,79; 7,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 9,36</t>
+          <t>-5,27; 8,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 4,91</t>
+          <t>-7,24; 5,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 7,29</t>
+          <t>-5,53; 7,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 5,07</t>
+          <t>-5,12; 4,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 1,44</t>
+          <t>-7,64; 0,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 5,04</t>
+          <t>-4,54; 4,79</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-68,63; 93,76</t>
+          <t>-67,58; 102,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-87,77; 6,3</t>
+          <t>-89,39; 20,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-59,9; 113,48</t>
+          <t>-56,46; 112,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-50,46; 259,25</t>
+          <t>-49,63; 224,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-73,87; 134,59</t>
+          <t>-73,07; 176,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-55,85; 197,61</t>
+          <t>-54,9; 224,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-45,02; 88,39</t>
+          <t>-44,72; 80,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-73,76; 26,28</t>
+          <t>-71,51; 20,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-44,41; 87,65</t>
+          <t>-41,31; 84,74</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-17,64; -1,89</t>
+          <t>-16,74; -0,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 0,39</t>
+          <t>-17,7; 0,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,75; -0,02</t>
+          <t>-16,38; 0,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 11,62</t>
+          <t>-3,59; 11,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 5,29</t>
+          <t>-8,81; 4,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 3,36</t>
+          <t>-9,18; 3,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 2,5</t>
+          <t>-8,73; 2,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,64; -0,17</t>
+          <t>-10,98; 0,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,19; -0,78</t>
+          <t>-11,39; -0,75</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-77,99; -9,29</t>
+          <t>-76,97; 0,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-74,51; 2,66</t>
+          <t>-76,18; 6,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-77,05; 5,03</t>
+          <t>-74,31; 3,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-34,38; 219,8</t>
+          <t>-31,13; 215,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-62,68; 123,9</t>
+          <t>-68,34; 84,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-73,69; 64,78</t>
+          <t>-72,87; 74,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-52,08; 27,01</t>
+          <t>-52,92; 27,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-63,58; 0,36</t>
+          <t>-63,93; 4,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-68,46; -6,49</t>
+          <t>-67,53; -4,42</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 1,34</t>
+          <t>-6,23; 1,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,03; -0,55</t>
+          <t>-7,75; -0,2</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,19; -0,93</t>
+          <t>-8,13; -0,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 3,43</t>
+          <t>-3,38; 3,51</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,2; -0,97</t>
+          <t>-7,59; -1,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,31; -1,21</t>
+          <t>-7,37; -1,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 1,12</t>
+          <t>-3,88; 1,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,88; -1,98</t>
+          <t>-6,7; -1,74</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,95; -2,04</t>
+          <t>-6,93; -1,95</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-45,46; 14,07</t>
+          <t>-45,41; 11,58</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-54,28; -4,24</t>
+          <t>-54,44; -0,01</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-55,66; -8,06</t>
+          <t>-56,97; -3,72</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-32,63; 39,54</t>
+          <t>-28,93; 43,2</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-62,73; -11,96</t>
+          <t>-63,7; -14,02</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-62,02; -11,9</t>
+          <t>-62,85; -11,88</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-31,7; 11,17</t>
+          <t>-31,61; 13,8</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-53,69; -18,39</t>
+          <t>-53,27; -17,23</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-56,04; -20,89</t>
+          <t>-55,45; -18,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C07-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP19C07-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-5,45</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-8,34</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-13,15</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-2,35</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-4,92</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-5,81</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-5,45</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-8,34</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-13,18</t>
+          <t>-5,8</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-9,8</t>
+          <t>-9,64</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 7,12</t>
+          <t>-14,67; 2,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 3,54</t>
+          <t>-16,38; 0,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,84; 3,49</t>
+          <t>-20,78; -6,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,71; 4,11</t>
+          <t>-10,79; 7,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,62; 0,59</t>
+          <t>-13,26; 3,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,52; -5,95</t>
+          <t>-14,17; 4,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 2,25</t>
+          <t>-10,09; 1,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,46; -0,32</t>
+          <t>-12,82; -1,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,37; -4,11</t>
+          <t>-14,98; -3,92</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-35,45%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-54,22%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-85,52%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-17,56%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-36,84%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-43,46%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-35,45%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-54,22%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-85,73%</t>
+          <t>-43,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-68,03%</t>
+          <t>-66,89%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-62,77; 84,25</t>
+          <t>-72,71; 37,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-72,11; 46,58</t>
+          <t>-81,84; 15,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-80,67; 49,75</t>
+          <t>-97,14; -50,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-69,57; 42,88</t>
+          <t>-61,47; 92,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-81,36; 19,57</t>
+          <t>-74,99; 41,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-97,0; -49,27</t>
+          <t>-78,66; 61,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-60,18; 22,96</t>
+          <t>-59,3; 18,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-72,0; -0,41</t>
+          <t>-71,93; -3,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-85,68; -29,67</t>
+          <t>-84,74; -32,15</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,73</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-6,23</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-3,45</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>2,56</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1,87</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,77</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,73</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-6,23</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,66</t>
+          <t>-2,6</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,19</t>
+          <t>-3,0</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 8,77</t>
+          <t>-6,15; 5,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 8,34</t>
+          <t>-11,43; -1,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 2,84</t>
+          <t>-8,84; 2,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 5,08</t>
+          <t>-3,53; 8,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,42; -1,56</t>
+          <t>-3,62; 8,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 1,71</t>
+          <t>-7,78; 3,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 5,46</t>
+          <t>-3,45; 5,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 1,65</t>
+          <t>-5,92; 2,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 0,8</t>
+          <t>-7,58; 0,8</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-7,85%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-67,2%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-37,22%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>31,86%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>23,23%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-34,52%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-7,85%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-67,2%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-39,53%</t>
+          <t>-32,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-36,86%</t>
+          <t>-34,63%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-37,34; 164,75</t>
+          <t>-54,04; 90,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-41,91; 176,58</t>
+          <t>-89,58; -18,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-75,11; 79,19</t>
+          <t>-71,82; 37,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-58,07; 77,98</t>
+          <t>-37,83; 160,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-89,81; -13,62</t>
+          <t>-38,65; 176,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,05; 30,79</t>
+          <t>-74,46; 74,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,03; 80,76</t>
+          <t>-33,63; 92,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-58,77; 26,39</t>
+          <t>-55,68; 33,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-65,07; 14,18</t>
+          <t>-66,23; 15,11</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,95</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-1,05</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,8</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-1,62</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-6,0</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,67</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,95</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-1,05</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,22</t>
+          <t>-0,01</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,95</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 5,23</t>
+          <t>-4,74; 8,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 0,47</t>
+          <t>-6,96; 5,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 7,01</t>
+          <t>-4,93; 8,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 8,22</t>
+          <t>-9,49; 5,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 5,8</t>
+          <t>-12,82; -0,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 7,2</t>
+          <t>-8,47; 7,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 4,93</t>
+          <t>-5,06; 5,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 0,87</t>
+          <t>-8,01; 1,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 4,79</t>
+          <t>-3,58; 6,14</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>28,29%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-15,21%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>26,06%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-16,1%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-59,49%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-6,6%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>28,29%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-15,21%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>-0,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-67,58; 102,0</t>
+          <t>-52,48; 219,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-89,39; 20,77</t>
+          <t>-70,49; 157,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-56,46; 112,62</t>
+          <t>-51,95; 235,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-49,63; 224,52</t>
+          <t>-65,98; 93,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-73,07; 176,96</t>
+          <t>-87,74; 11,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-54,9; 224,5</t>
+          <t>-58,22; 143,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-44,72; 80,72</t>
+          <t>-46,04; 88,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-71,51; 20,07</t>
+          <t>-72,22; 23,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-41,31; 84,74</t>
+          <t>-35,85; 110,22</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,54</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,47</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-2,17</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-9,19</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-8,56</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-8,75</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,54</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,47</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,58</t>
+          <t>-8,73</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-5,88</t>
+          <t>-5,61</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-16,74; -0,56</t>
+          <t>-3,86; 11,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-17,7; 0,09</t>
+          <t>-8,13; 4,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,38; 0,06</t>
+          <t>-8,72; 4,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 11,03</t>
+          <t>-17,06; -0,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 4,46</t>
+          <t>-17,5; -0,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 3,25</t>
+          <t>-16,9; -0,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 2,54</t>
+          <t>-8,44; 3,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 0,09</t>
+          <t>-10,02; 0,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,39; -0,75</t>
+          <t>-10,42; -0,14</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>40,49%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-16,85%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-24,84%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-52,02%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-48,42%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-49,51%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>40,49%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-16,85%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-29,5%</t>
+          <t>-49,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-44,0%</t>
+          <t>-42,0%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-76,97; 0,3</t>
+          <t>-33,59; 222,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-76,18; 6,41</t>
+          <t>-63,02; 108,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-74,31; 3,29</t>
+          <t>-70,44; 87,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-31,13; 215,1</t>
+          <t>-77,88; -2,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-68,34; 84,37</t>
+          <t>-74,73; 5,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-72,87; 74,15</t>
+          <t>-74,26; 4,43</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-52,92; 27,9</t>
+          <t>-52,51; 32,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-63,93; 4,97</t>
+          <t>-64,1; 3,14</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-67,53; -4,42</t>
+          <t>-65,84; -0,7</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,14</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-4,34</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-3,96</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-2,54</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-4,05</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-4,47</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,14</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-4,34</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-4,26</t>
+          <t>-4,28</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-4,46</t>
+          <t>-4,18</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 1,17</t>
+          <t>-3,88; 3,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,75; -0,2</t>
+          <t>-7,89; -1,37</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,13; -0,42</t>
+          <t>-7,66; -0,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 3,51</t>
+          <t>-6,7; 1,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,59; -1,17</t>
+          <t>-7,99; -0,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,37; -1,02</t>
+          <t>-8,17; -0,55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 1,36</t>
+          <t>-3,82; 1,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,7; -1,74</t>
+          <t>-6,61; -1,63</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,93; -1,95</t>
+          <t>-6,78; -1,81</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-1,37%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-43,3%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-39,55%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-20,81%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-33,16%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-36,59%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-1,37%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-43,3%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-42,53%</t>
+          <t>-35,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-40,13%</t>
+          <t>-37,62%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-45,41; 11,58</t>
+          <t>-32,19; 41,55</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-54,44; -0,01</t>
+          <t>-64,08; -14,62</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-56,97; -3,72</t>
+          <t>-61,28; -8,3</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-28,93; 43,2</t>
+          <t>-46,71; 11,65</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-63,7; -14,02</t>
+          <t>-56,74; -4,1</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-62,85; -11,88</t>
+          <t>-56,65; -2,17</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-31,61; 13,8</t>
+          <t>-30,64; 13,27</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-53,27; -17,23</t>
+          <t>-52,34; -16,19</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-55,45; -18,78</t>
+          <t>-54,68; -19,02</t>
         </is>
       </c>
     </row>
